--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,9 +783,1498 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136707330</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>325234</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6557584</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707330</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136707331</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>325219</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6557575</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707331</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136707338</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>325148</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557681</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707338</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136707356</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>325130</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6557731</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707356</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136707357</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>325074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6557731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707357</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136707335</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92127</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>325168</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557621</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707335</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136707337</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325154</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557663</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707337</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136707334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325154</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6557632</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707334</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136707336</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>325154</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557663</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136707359</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325057</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6557745</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707359</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136707333</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325154</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557632</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707333</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136707358</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>325057</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557745</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707358</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136707355</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325113</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557751</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707355</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>136707355</v>
       </c>
       <c r="B15" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -1558,11 +1558,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -1680,11 +1676,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -1802,11 +1794,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -1924,11 +1912,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -2046,11 +2030,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -2168,11 +2148,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22947-2026 artfynd.xlsx
+++ b/artfynd/A 22947-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>136707330</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>136707331</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>136707338</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>136707356</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136707357</v>
       </c>
       <c r="B7" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136707335</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136707337</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>136707334</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136707336</v>
       </c>
       <c r="B11" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>136707359</v>
       </c>
       <c r="B12" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136707333</v>
       </c>
       <c r="B13" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136707358</v>
       </c>
       <c r="B14" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>136707355</v>
       </c>
       <c r="B15" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
